--- a/MATLAB/test_data/MATLAB_test_record.xlsx
+++ b/MATLAB/test_data/MATLAB_test_record.xlsx
@@ -1626,7 +1626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2433,7 +2433,199 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>IRRECONCILABLE chi_r_x conflict; root = the 1/z-inflated s_ddot</t>
+          <t>light-s_ddot wall; reduce chi_r_x next</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>CB25</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>cb_skept_redux/07/cont/t15</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>KEEP s_ddot via HEAVY LPF: reduce chi_r kills divergence; tau=1.5 + chi_r=0.85</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>reduced chi_r=0.7 STABLE(21/25 no breach); full s_ddot still diverges; Gamma_x diverges; tau=1.5 removes 1/z spike keeps smooth target-accel FF -&gt; chi_r climbs to 0.85 -&gt; 25/25 SP + 74/75 noisy, no breach</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>KEEP-s_ddot reaches 25/25 via heavy tau1.5; BUT see CB29 (damped cycle, not converged)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>CB26</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>cb_ztaper* (REVERTED)</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>z-taper: scale s_ddot by min(1,alt_above/z_ref) -&gt; cancel 1/z terminal over-drive, NO lag</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>low tau=0.5 + z_ref=2.0 -&gt; 24/25 noiseless + 75/75 noisy, no breach; responsive FF fixes Liss IC3 noisy miss. BUT uses ALTITUDE</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>INVALID: scale-free/unknown-depth premise -&gt; reverted to commit a152479</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>CB27</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>cb_lt_peraxis/traj</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Per-axis + terminal-phase trajectory: WHY do low-tau cells fail?</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>NOT offset/lag -&gt; FORCED LIMIT CYCLE: lateral osc ~1Hz +-0.1m/+-0.3m/s locked to |h_d_lat| 0.07-&gt;0.6; touchdown catches random phase. Residency LOW (interior, not funnel-limited)</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>failures are a forced under-damped cycle, not a tunable offset</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>CB28</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>cb_damp/sens/cap/flowfilt</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Lever exhaustion: which control param damps the velocity cycle?</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>NONE. chi_r damps position-amp not velocity (forcing-set); p_r/p_2inf/cap(no bite)/gamma_2/E/N/kappa flat or diverge; optical-flow filter CB_SDOT_FILT partial-damp but lag diverges fast cell (Liss IC3), never SP; h_d filter wrong point (drop keeps h_d, no cycle)</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>velocity amplitude is s_ddot-FORCING-set; only filter the forcing (lag) or drop</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>CB29</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>cb_traj_cmp</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Does heavy-tau converge or limit-cycle? vs drop terminal trajectory</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>heavy-tau = DAMPED cycle ~0.25 (not converged, passes by phase luck); DROP more damped ~0.16 -&gt; more margin -&gt; 75/75 vs 74/75; s_ddot FF re-injects cycle energy even at tau1.5</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>DROP is the scale-free OPTIMUM (most damped); heavy-tau = drop+leftover forcing</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>CB30</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>cb_root</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Root of the underlying cycle (present even in drop)</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>under-damped lateral loop: sigma_x osc +-0.14 but |sigma|&lt;&lt;E=1.0 ALWAYS -&gt; switching linearized away -&gt; no nonlinear damping; eR~0.15rad &gt; commanded tilt 0.10rad -&gt; INNER-LOOP attitude lag (cascade-bw mismatch)</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>root = inner-loop attitude lag suspected; kR/kOmega + E test PENDING</t>
         </is>
       </c>
     </row>

--- a/MATLAB/test_data/MATLAB_test_record.xlsx
+++ b/MATLAB/test_data/MATLAB_test_record.xlsx
@@ -1626,7 +1626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2629,6 +2629,678 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>CB31</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>cb_kr_asym/kx_finish</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Inner-loop speedup on responsive keep-s_ddot: kR/kOmega up, then per-axis kR split</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>kRx2 KR=[3;3;0.5] KOmega=[0.6;0.6;0.1] + tau0.7 -&gt; 17/25-&gt;24/25 no breach (only Liss IC3 vel0.273). ASYMMETRIC kR_y&lt;3 is a DEAD END: 'fixes' Liss IC3 only by detuning into another limit-cycle basin (sharp Hopf bistability; ky2.0 damped, ky2.25 pumped 0.41) but FULL 5x5 breaks Static IC3/IC5 + Circ IC4/IC5 -&gt; 18-19/25; 6-cell probe missed collateral</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>kR raises stability margin (helps) but cycle persists; asymmetric kR illusory</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>CB32</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>cb_tau_finish</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Heavy tau at symmetric kR=[3;3;0.5] (collateral-free lever)</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>tau 0.9-&gt;24/25, tau1.0-&gt;24/25, tau1.2-&gt;25/25, tau1.5-&gt;25/25 (no breach, worstResid0.618). Liss IC3 0.27-&gt;0.12. Deterministic 25/25 keeping responsive s_ddot -- but see CB33/CB34 (phase luck)</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>deterministic 25/25 via heavy tau -- NOT a real fix</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>CB33</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>cb_noisy_resp</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>NOISY validation of the responsive tau1.2 25/25 config, 4 seeds x 5x5</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>83/100 SP (seeds 25,25,24,9), 96/100 land, worstResid 2.014 (FUNNEL BREACH). Liss IC3 vel jumps 0.066-&gt;1.452(sd3)-&gt;3.781(sd4). Deterministic 25/25 -&gt; fragile under noise</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>responsive tau config NOT bakeable -- phase-fragile</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>CB34</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>cb_cause/phase/lag_probe</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>MECHANISM: is tau damping the cycle or its effect? Measure the FF's damping sign</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>FF magnitude is BOUNDED ~0.4 (capped, NOT 1/z-exploding). corr(-FF_x,vx)=+0.64 KEEP vs -0.50 DROP -&gt; s_ddot FF is ANTI-DAMPING (injects power in phase with velocity, mean(FF*vx)=+0.044&gt;0). Net corr(a_actual,vx)=-0.02 KEEP (~zero net damping=sustained) vs -0.18 DROP (decays). tau sweep: corr(-FF,vx) +0.77(0.5)-&gt;0.00(1.5) ONLY by attenuating FF toward zero; no tau keeps FF AND healthy damping. FF intrinsic positive-feedback on ego-velocity (h=v/z)</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>ROOT = FF anti-damping cancels natural damping. DROP (remove FF) is the UNIQUE complete elimination -- restores -0.18 damping -&gt; cycle decays. 25/25+75/75. Drop default stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>CB35</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>cb_keep_noisy</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>KEEP s_ddot directive: noise-validate the tau where FF stops anti-damping (tau1.5, corr=0); CB33 only tested tau1.2</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>tau1.5 (and 1.8): noiseless 25/25 but NOISY 83/100 -- seeds 1,2 clean, seeds 3,4 blow up Liss IC3 (2.0,3.8), breach 2.09. Removing the NOISELESS anti-damping is not enough: net damping only -0.04 (vs drop -0.18) -&gt; noisy s_ddot FF re-excites the barely-damped cycle. No tau saves keep-s_ddot under noise</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>keep-s_ddot is noise-fragile at EVERY tau; needs ADDED damping, not just de-anti-damping</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>CB36</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>cb_asym_diag/koy/koy_noisy</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>WHY asymmetric kR fails + find a compensating param (user directive, keep s_ddot)</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Asymmetric kR=[3;2;0.5] fails MIXED-axis: Static/Linear on X (0.20-0.26), Circ on Y (0.28-0.31); Liss IC3 itself bistable. Compensator = kOmega_y=0.10 (LOW Y attitude-rate gain detunes the Y resonance; p2inf_y nearly irrelevant, 0.35 vs 0.50 both work) -&gt; FULL 5x5 25/25 noiseless, no breach (resid 0.610), KEEPING s_ddot. BUT NOISY 85/100 -- seed4 Liss IC3-&gt;5.22, breach 1.51, 21/25 land. Same wall as CB33/CB35</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>per-axis gains (kR_x, kOmega_y, p2inf_y) RELOCATE the resonance to deterministic 25/25 but DON'T add net damping -&gt; can't beat the ~83-85/100 noise wall. Robust keep-s_ddot needs explicit added damping (e.g. scale-free flow-damping -k_d*h), not gain redistribution</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>CB37</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>cb_param_damp</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>WHICH control param reduces the cycle? One-at-a-time sweep on Liss IC3, metric = netDamp corr(a_actual,vx) + terminal pp(vx) (cycle itself, not pass/fail)</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Ranked by net damping (keep s_ddot, baseline netDamp=-0.02): chi_r=0.5 -&gt; -0.28 (STRONGEST), kR_xy=4 -&gt; -0.18 (= DROP ref), DROP -0.18. NON-levers: kOmega_xy &amp; E_xy only shrink amplitude (netDamp~0); raising Gamma_xy/gamma2/chi_r=1.2 DIVERGES (boundary-layer destabilize); default kR_xy=1.5 diverges keep-s_ddot. Consistent w/ CB10 (chi_r0.5) + CB30 (kR damping route)</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>ONLY chi_r(lower~0.5) and kR_xy(raise~4) add net damping while keeping s_ddot; chi_r strongest. Both have global tradeoffs (chi_r0.5 costs Circ precision CB11; kR4 over-damps CB18) and neither alone beats the noise wall -&gt; combine for margin</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>CB38</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>cb_combine_damp/seed4_diag/p2z</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>COMBINE the two damping levers (chi_r-lower + kR_xy-raise) vs noise wall; per-axis decompose the residual; add descent-axis lever</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Symmetric stack chi_r=0.65 kR_xy=4 keep-s_ddot: noiseless 25/25 no breach -&gt; NOISY 89/100 (seeds1-3 PERFECT 25/25, up from 83-85 wall; seed4=14/25). Per-axis decomp of seed4: the wall is DESCENT(vz)-DOMINATED -- ~8 cells fail pure-vz~0.20 (noise inflates terminal descent 0.10-&gt;0.20), only 2 are lateral-LC catastrophes (Liss IC3 vx1.06/vy2.08 breach 1.70; Static IC5 vz2.09). Added P2INF_Z_OVERRIDE hook (test-only, default p_2inf(3)=1.5 unchanged); tighten 1.5-&gt;1.0 = vz margin -&gt; 92/100 (seed4 17/25), 0.7 no better. Residual = Liss IC3 lateral divergence (noise-excited), gain-margin tuning can't remove</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>stacked damping + descent-margin: keep-s_ddot 83-&gt;89-&gt;92/100. chi_r-low+kR-high makes 3/4 seeds perfect; descent lever P2INF_Z=1.0 best. Remaining wall = noise-excited Liss IC3 lateral divergence; still &lt; drop 75/75-equiv robustness</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>CB39</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>cb_push_liss/liss_trace/p20/yaw_perf</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>PUSH the residual seed-4 Liss IC3 breach (chi_r_x-lower, early flow funnel p_20-lower); TRACE the cycle; YAW perf check</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>(1) chi_r_x LOWER backfires: [0.55;0.65]-&gt;81, [0.50;0.65]-&gt;78 (de-weights zeta_r -&gt; noise-fragile, regresses other cells); chi_r=0.65 is the noise floor. kR_x&gt;4 over-stiffens (CB37). (2) TRACE Liss IC3 seed4: cycle IGNITES AT ALTITUDE (vy-&gt;1.84 @4m, t=1.5s), rotates X&lt;-&gt;Y (coupled 2-D mode), partial mid-descent recovery, then terminal divergence (|v|2.6, breach@t3.54). NOT terminal-margin -- a noise-ignited GROWING oscillation = the s_ddot anti-damping pump under worst-case seed. (3) p_20_xy tighten DOES kill it (seed4 2.76-&gt;0.19 @p_20=14!) but over-constrains all else -&gt; 65/100; tighter breaches on IC offset. (4) YAW HEALTHY: noiseless terminal |e_a|&lt;2.5deg all cells, bounded |u_a|&lt;1.6, kappa_a&lt;0.24 (peaks are IC3 initial-acquisition transients); on diverging seed4 yaw dragged to 27.8deg but u_a/kappa_a stay bounded -&gt; yaw is a VICTIM of the lateral cycle, not a cause</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>92/100 is the keep-s_ddot CEILING: residual is suppressible only by global over-constraint (p_20=14 fixes Liss IC3 but wrecks 65/100). Yaw not implicated. Confirms only DROP removes the pump cleanly</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>CB40</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>cb_funnel_cause</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>WHY does p_20-tighten kill Liss IC3 but wreck the rest? Measure flow-funnel OCCUPANCY (|V_h_e|/p_2) -- is it containment or gain?</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>NOT containment: legit flow error |V_h_e_xy|=0.18-1.13 -&gt; funnel occupancy only 0.01-0.10 at p_20=25; even the Liss IC3 seed4 DIVERGENCE peaks at |V_h_e|=2.39 = occupancy 0.20. The flow error NEVER nears the funnel. Real mechanism: barrier gain G_2 = (e^z2+1)^2/(2 e^z2 p_2) ~ 1/p_2 -&gt; p_20 is covertly a LOOP-GAIN knob. Tightening raises flow-loop gain everywhere: enough authority to damp Liss IC3's s_ddot pump, but into the cascade lag it over-drives the other cells (p_20=14 noiseless breach resid1.48 is a POSITION breach from over-aggressive control, not a flow breach; monotone worse 10-&gt;5.9). Same gain-vs-lag tradeoff as Gamma/gamma2 (CB37)</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>UNIFIES the keep-s_ddot campaign: residual = authority/damping deficit curable only by raising loop gain (p_20/Gamma/kR/chi_r all gain knobs), but cascade phase-lag caps global gain -&gt; no single gain damps Liss IC3 AND keeps the lag-limited cells. Structural no-free-lunch. Only DROP escapes (nominal gain already has +damping margin w/o the pump)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>CB41</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>cb_seed4_z</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Re-identify the 8 failures of the 92/100 config (all on seed 4): per-axis + cause classify</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Split 5 DESCENT / 3 LATERAL -- the s_ddot pump acts on the Z axis too, not just laterally. TWO divergences on DIFFERENT axes: Static IC5 = DESCENT blow-up (vz=2.19 breach 1.10; IC5=[2,2,-3] low start -&gt; vertical s_ddot 1/z-inflated ignites) -- earlier mislabeled lateral; Liss IC3 = LATERAL blow-up (vx/vy=2.76 breach 1.91). Plus 6 marginal: 4 descent vz~0.19-0.22 (p2inf_z=1.0 reduced but didn't kill), Sin IC3 lateral 0.53, Circ IC4 lateral 0.29</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>92/100 residual is a TWO-AXIS s_ddot pump (lateral AND descent), descent the larger share (5/8). Beating it needs +damping margin on BOTH loops simultaneously -- cascade-lag-capped gain (CB40) can't do that globally. Reinforces: only DROP escapes</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>CB42</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>cb_zdamp/zfix</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>WHICH gain removes the Z (descent) limit cycle? Added Z-SMC override hooks (GAMMA_Z/E_Z/CHIZ/GAMMA2_Z/KAPPA0_Z, test-only); netDamp(az,vz) sweep + full-noisy validate</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>On Static IC5 seed4 (descent DIVERGENCE vz-&gt;2.19) baseline netDamp=+0.45 (strongly anti-damped). Only Gamma_z(descent sliding gain) reduces it (+0.45-&gt;+0.19 @3.0), then gamma2_z-low (+0.29) and chi_z-low (+0.37) -- but NONE crosses to net-damped, all still diverge. Full-noisy: Gamma_z=2.5 BREACHES noiseless (22/25 resid1.5) -- raising descent gain into the descent-loop lag (I_a_cd LPF tau0.08 + s_ddot_z pump) over-drives = same gain-vs-lag wall (CB40); gamma2_z=0.1-&gt;84 (worse), chi_z=0.012-&gt;91 (~same)</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>NO control gain robustly removes the Z cycle while keeping s_ddot. Gamma_z is the right DIRECTION (descent damping lever, analogue of lateral kR) but gain-capped -- destabilizes before it damps. Confirms two-axis structural ceiling: s_ddot pump corrupts BOTH loops, neither escapes gain-vs-lag. Only DROP gives nominal Gamma_z=0.75 a +damping margin</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>CB43</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>cb_zclass</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>WHY each Z gain fails -- classify by mechanism on a BOUNDED noiseless descent cycle (Static IC5): netDamp + authority std(a_z) + vz freq</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Several Z gains DO reach net damping noiseless: kappa0_z=0.5 (-0.24), E_z=0.3 (-0.07, freq 0.10-&gt;0.30=stiffness), p20_z=2 (-0.09), chi_z=0.10 (+0.12=integral). Gamma_z=3 does NOT damp (+0.49) -- authority EXPLODES std(a_z) 0.1-&gt;5.0 (chatter). Each damping mechanism becomes a NOISE LIABILITY: Gamma_z=chatter/over-drive; kappa0_z=adaptive-gain RUNAWAY on funnel breach (documented kappa_z runaway, N_z 0.05-&gt;0.02); E_z=hard-switching chatter; chi_z=integral WINDUP during divergence; p20_z/gamma2_z=G2 gain over-drive + lost terminal bound</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>ROOT: descent surface sigma_3 = zeta_2(3)+chi_z*int has NO direct vz-damping term -&gt; damping must be SYNTHESIZED via switching/stiffness/integral/funnel gain, each of which amplifies the noisy 1/z flow + s_ddot pump as much as the damping. Same knob that quiets the clean cycle ignites the noisy one (chatter/windup/runaway/over-drive). No Z gain survives to net damping under noise</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>CB44</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>cb_zcombo</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>How to control kappa_z runaway + can a COMBINATION of descent gains tune it? Pair damping lever (kappa0_z) with anti-runaway (KAPPA_MAX_Z cap + leakage P_z); added P_Z_OVERRIDE hook</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>kappa ODE: dk/dt=Theta_norm*N*G*|sigma| - N*P*k; drive explodes on breach (G2,|sigma|-&gt;big), leakage N*P=0.1 too weak. CONTROL: cap (KAPPA_MAX_Z) + raise P_z DOES bound it -- cap0.4+P_z20 cut worstResid 1.905-&gt;1.307 (lowest of any keep-s_ddot cfg), no catastrophic blow-up. BUT SP 92-&gt;86: capping low enough to stop runaway STARVES legit descent authority the marginal cells need (same kappa is both the runaway AND the needed gain -&gt; confirms MT2 clamp-0.5-didnt-fix). COMBINATIONS (kappa0_z.5+cap+P_z+Gamma_z) all 86-90/100, none beats simple 92</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>kappa_z runaway IS controllable (projection cap + leakage) but it is a SYMPTOM of the breach (s_ddot pump), not the cause -&gt; bounding it doesnt recover SP. Combinations dont escape: descent levers are COUPLED through the same authority-vs-lag / damping-vs-runaway constraint (kappa damps AND runs away; capping kills both). No combo relaxes the constraint -&gt; 92/100 keep-s_ddot ceiling stands; only DROP removes the forcing</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>CB45</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>cb_smooth/descent_cause/drop4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>SMOOTH DESCENT: which param removes/bounds the Z cycle? + FAIR drop-vs-keep over 4 seeds</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>BOMBSHELL: Static IC5 seed4 descent blows up (peak|vz|~2.0, land=0) under EVERY config -- keep, cap+P, DROP, all kR(1.5-4)/chi_r(.65-.85)/p2inf_z(1-2.5) -&gt; NOT the s_ddot pump, NOT tunable; a PATHOLOGICAL noise seed (unrecoverable descent transient, needs perception/flow-outlier handling). FAIR 4-seed comparison: baked DROP = 82/100 (seeds 25/25/24/8) vs keep-s_ddot 92-config = 92/100 (25/25/25/17). The drop '75/75 strictly better' was a SEED ARTIFACT (CB16 used seeds 1-3 only; seed4 never tested). Over the hard 4-seed set keep-s_ddot stacked-damping BEATS drop. Seeds 1-3 descend SMOOTH (peak|vz| 0.5-0.66) in all configs</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>MAJOR CORRECTION: keep-s_ddot (chi_r=0.65,kR=4,p2inf_z=1.0,KAPPA_MAX_Z+P_z) is NOT worse than drop -- it WINS over 4 seeds (92 vs 82). Smooth descent IS achieved on all recoverable seeds by chi_r-low+kR-high+p2inf_z margin (+kappa cap backstop). The lone residual (Static IC5 seed4) is a noise outlier beyond ANY control gain incl drop -&gt; perception-layer problem, not control</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>CB46</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>cb_s5_trace/cbf_audit</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Static IC5 seed4 REAL failure mechanism (signal trace) + CBF performance audit across runs</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>MECHANISM (trace, DROP to isolate): descent guidance des h_z=-0.42 const -&gt; demands vz=0.42*z (~1.2m/s @3m, aggressive, SHARED by all configs = h_rd setpoint). Descent under-damped -&gt; vz OVERSHOOTS profile (vz1.28 vs des0.66 @z1.57). TRIGGER @t2.1 (altGap1.5m): measured optical flow h_z SIGN-FLIPS -0.39-&gt;+0.42 (gross perception error, 1/z-amplified pixel noise at high vz). Controller trusts it -&gt; cuts thrust 20-&gt;2.9 + leans 30deg tilt (robs vertical thrust) -&gt; vz runaway 2.1, no land. NOT s_ddot pump (drop fails too), NOT kappa_z runaway (kz stayed 0.22-0.34), NOT funnel (occ&lt;0.27). It is a PERCEPTION failure (flow outlier) -&gt; no control GAIN fixes it (all consume the bad measurement). Fix upstream: flow innovation/outlier gating, gentler h_rd, or velocity-aware flow (matches PERCEPTION_FLOW_FINDINGS ~2m/s range). CBF AUDIT: cbf_ok ~100% all runs, ~0%% hard-clamp, never saturates; actual tilt overshoots cone &lt;=9deg on IC3 acquisition (absorbed by 15px inset); visibility HELD on all successes; CBF not implicated in any failure (Static IC5 s4 tilt 30deg still cbf_ok)</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Static IC5 seed4 = PERCEPTION (flow sign-flip outlier) + aggressive h_rd, NOT control -&gt; perception-layer fix only. CBF performs correctly throughout (feasible ~100%, inset absorbs tilt overshoot, not a failure source)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>CB47</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>cb_loom/pinvtol/pinvtol2/tol_cycle</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>REAL cause of the h_z sign-flip + user lever pinv(L_s,TOL) 2nd-arg tuning + why low tol fails rest (limit cycle)</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>h_z(loom) recovered by pinv(L_s,4)*dPdt; vz column of L_s=[-x;-y], loom is the WEAKEST singular mode. LOOM TRACE Static IC5 s4: pinv under-reports true h_z (err+0.20) then SIGN-FLIPS at featRad&gt;1.2 (marker fills/overflows FoV near ground, NOT centering); corr(featRad,|err|)=+0.85. CAUSE = tol=4 TRUNCATES the weak loom SV (an SV sits in (1,4]). pinv TOL is a real lever: tol&lt;=1.5 RETAINS loom -&gt; Static IC5 s4 LANDS (peak|vz| 2.1-&gt;1.19). BUT global tradeoff: tol4=92/100 S5s4 blows up; tol1.5=88 S5s4 lands; tol0.01=44 (15/25 even NOISELESS). WHY rest fail (LIMIT CYCLE confirmed, Lis-IC4 noiseless): low tol UN-REGULARIZES pinv -&gt; tiny SV divides finite-diff/quant error in dPdt -&gt; loomErr 0.03-&gt;0.29 (10x) -&gt; descent vz pp DOUBLES 0.70-&gt;1.57, freq DOUBLES 0.17-&gt;0.33Hz -&gt; fail. Regularization-vs-resolution (truncated-SVD/Tikhonov) tradeoff</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>pinv TOL = regularization knob on the ill-conditioned loom mode. High tol regularizes (clean, no cycle) but loses loom where critical (S5s4 runaway); low tol resolves loom (fixes S5s4) but amplifies error -&gt; descent limit cycle on the rest. SAME wall, perception layer. REAL fix = well-conditioned loom measurement (direct apparent-size/area rate), NOT a tolerance value. Added PINV_TOL + loom-diag log hooks (test-only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>CB48</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>(loom root-cause: cb_loom/sv/pinvtol)</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>DESCENT root cause: V_h(3) loom = vz/z FLOW DIVERGENCE, recovered as the 3rd row of pinv(L_s)*dPdt; vz column of L_s=[-x;-y] is the WEAKEST singular mode (sigma_min~2.09, in (0.01,4] 93%% of steps)</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>pinv(L_s,TOL) tol=4 TRUNCATES the loom SV -&gt; h_z under-reports + SIGN-FLIPS near ground (Static IC5 s4 descent runaway). tol&lt;=1 RETAINS it (fixes S5s4) but un-regularizes -&gt; amplifies dPdt finite-diff error -&gt; descent LIMIT CYCLE (Lis-IC4 noiseless: vz pp/freq DOUBLE) -&gt; suite 44/100. Regularization-vs-resolution (truncated-SVD) tradeoff; no single tol wins. SG-derivative dPdt to cut noise = fatal LAG (0/25)</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>loom failure = ill-conditioned pinv weak-mode, NOT noise per se. Fix = estimate loom WITHOUT pinv (area-rate divergence). gyro can't de-rotate (target rotates) but AREA is rotation-invariant (curl+shear area-preserving) -&gt; loom decoupled</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>CB49</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>cb_momverify/momval/calib</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>SCALE-FREE moment loom: V_h(3) = -1/2 d(ln M)/dt, M=2nd-moment corner spread (fractional rate -&gt; size/depth-invariant, fixed 1/2, no cal). Gated USE_MOMENT_LOOM (default off)</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED vs analytical truth: slope 0.90-0.99 CONSISTENT across cells (=scale-free), corr 0.86-0.98. CALIBRATION beats pinv loom esp noisy (corr 0.918 vs 0.865, RMS 0.049 vs 0.062). CLOSED-LOOP keep-s_ddot 92-config: noiseless 25/25 (no regression) -&gt; NOISY 92-&gt;95/100, breach 1.91-&gt;1.49. Residual = pre-existing pathological seeds (Static IC5 s4, Liss IC3 s4), NOT loom-caused</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>moment area-rate loom is the validated win: better-calibrated + noise-robust + scale-free + decoupled (no sigma~2). 95/100. Opt-in via USE_MOMENT_LOOM=1; baked default unchanged</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>CB50</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>cb_momflow/momdiag/path/latfit/redlat/calib</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Replace pinv COMPLETELY? Lateral V_h(1:2) from centroid (1st moment) and from reduced-pinv (loom col removed). Calibrate all estimators vs truth</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>In C_SIMPLE+combined-barrier ONLY V_h uses pinv (V_w/V_dw dead; angular=gyro psi_dot_b). Full moment FLOW (centroid lateral) REGRESSES 95-&gt;86: centroid POORLY CALIBRATED (slope 0.71 corr 0.72 noisy), diverges on IC3/moving cells. CAUSE of pathological-seed lateral divergence = pinv CROSS-CONTAMINATION (joint 6-DOF lsq spreads loom-noise into lateral; over-reads Static IC5, under-reads Liss IC3). Reduced-pinv lateral (loom col removed) WELL-calibrated (slope 1.02 corr 0.83 = pinv) but closed-loop 90 (filtering diff) + STILL doesnt land pathological seeds. alpha-rate de-rotation: ZERO effect (d=0.001)</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Lateral is the pinv GOOD part (well-conditioned, 4-corner-fused); every replacement regresses (centroid 86, reduced 90). Pathological seeds fail under ALL estimators (raw terminal noise/FoV-overflow, a FRONT-END limit). VERDICT: hybrid = moment loom + pinv lateral = 95/100 is the right architecture; dont replace lateral</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>CB51</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>cb_loomgain</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Apply scale-free lag-comp gain to moment loom (slope~0.82 -&gt; aim 1.0)? Sweep MOMENT_LOOM_GAIN</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>gain=1.0 -&gt; 95/100 (BEST); 1.1-&gt;91; 1.2-&gt;88 (nl 24/25); 1.3-&gt;84 (breach 2.2). Compensation HURTS monotonically</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>the slope~0.82 under-read is BENIGN -- controller gains already tuned around the in-loop filter attenuation. Scaling the loom up over-drives descent -&gt; regression. KEEP raw moment loom (gain=1.0). FINAL: moment loom = 95/100 optimum</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/MATLAB/test_data/MATLAB_test_record.xlsx
+++ b/MATLAB/test_data/MATLAB_test_record.xlsx
@@ -1626,7 +1626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -3301,6 +3301,134 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>CB52</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>cb_chi/kr/komz bake (VDF_ASMC clean blocks)</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Cycle-damping gain campaign on the clean single controller. chi_r 0.85-&gt;1.15 (full +-40%); kR-roll 1.5-&gt;2.5 (Y-attitude damping); kOmega_z 0.1-&gt;0.2</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>chi_r=1.15 (4b87e20): full +-40% guaranteed, keeps 25/25. kR=2.5 (c383a64): SHARP optimum (2.0 near-divergent, 4.0 collapse), damps Y-lateral cycle. kOmega_z=0.2 (783f462): the ROOT fix -- per-axis map found YAW cycle (Circ-IC3=1.78) PUMPS the lateral cycles via yaw&lt;-&gt;image coupling; 0.2 kills yaw -90% AND lateral (Y 0.98-&gt;0.11) MONOTONICALLY, zero gate cost. All bit-exact blocks-vs-canonical |delta|=0</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>kOmega_z (yaw rate damping) is the master cycle lever -- CHECK YAW FIRST on any lateral-cycle problem. kR=2.5 sharp = robustness risk. Per-axis cycle map: Z-descent 0.48 now largest (irreducible)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>CB53</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>cb_hrd floor + revert (60ac526-&gt;593f0d6)</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>h_rd 0.42-&gt;0.40 to shrink the descent cycle (deep sweep flagged h_rd as the only lever moving the descent floor)</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>h_rd=-0.40 shrinks descent cycle -21% (0.48-&gt;0.375), CLEAN on seeds 1,2,3 (real 25/25). BUT comparison regen (seed 1002) exposed catastrophic fly-aways (vel 33!). Reverting h_rd-&gt;-0.42 fixed seed1002 (5/5) + broad robustness 51/55 vs 46/55. Gentler/slower descent spends MORE time in low-alt 1/z danger zone -&gt; more fly-aways</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>h_rd=-0.42 STANDS. Smaller cycle != more robust. LESSON: validate gains across a SEED ENSEMBLE, not seed1+noiseless -- the campaign shipped a fragile h_rd by optimizing on seed1</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>CB54</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>cb_flyaway/fa2/spike2 (trace)</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>WHY does the quadrotor fly away? Trace Linear-IC2 seed1004 (vel 23.7)</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>NOT a slow drift, NOT a noise outlier. Drone descends CLEANLY 31s to alt 0.33m (0.13m above zf=0.20), then LAUNCHES upward (alt 0.33-&gt;16m, descVz=-22.79). dPdt ramps GRADUALLY 161-&gt;472 (not a discrete jump); baseline dPdt~200 at 0.35m = 7x noise floor (geometry not noise). V_h(3) ramps WHILE altitude reverses = POSITIVE FEEDBACK. Root = terminal 1/z geometric instability: loom V_h(3)=vz/z has loop gain proportional 1/z-&gt;inf near touchdown; self-excites (V_h(3)up-&gt;thrust-&gt;ascent-&gt;dPdt up-&gt;V_h(3) up). Noise SEEDS it, geometry provides the gain; a race descent-to-zf vs loop igniting</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>FLY-AWAY = terminal 1/z positive-feedback launch, a PERCEPTION-FRONT-END limit (same 1/z wall as lateral precision). Explains seed-dependence + the h_rd paradox (gentler=more danger-zone time). Fix = bound V_h(3) or fix the regulation</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>CB55</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>cb_hez (h_ez convergence)</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>User insight: regulating the loom should make d(area)/dt constant (dPdt flat, not ramping). Is h_ez=V_h_e(3) converging to 0?</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>NO. V_h_d(3)=-0.42 (correct, constant) but V_h(3) only reaches ~-0.3 -&gt; persistent h_ez ~+0.12 in BOTH clean AND fly-away. The descent loom is regulated to ~-0.3, NOT commanded h_rd=-0.42 -&gt; loom NOT constant -&gt; area rate NOT constant -&gt; dPdt RAMPS -&gt; enables the 1/z instability. Root = weak descent integral (chi_z=0.025 + izeta2_max=5 clamp -&gt; max authority ~0.125, can't null steady-state loom error). kappa CAN'T help: 1/z spike enters u_eq c-term -h_z*h (quadratic), bypasses u_sw/kappa; kappa assumes sigma correctly measured (this is sensor-side)</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>h_ez non-convergence is the ROOT regulation defect behind the fly-away. PROPER fix = strengthen descent integral so h_ez-&gt;0 (constant loom = constant area rate = scale-free soft touchdown); band-aid = LOOM_CLAMP V_h(3) before SG filter (gated, default-off). Descent-integral (chi_z/izeta) strengthening prototype in progress</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/MATLAB/test_data/MATLAB_test_record.xlsx
+++ b/MATLAB/test_data/MATLAB_test_record.xlsx
@@ -1626,7 +1626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -3429,6 +3429,166 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>CB56</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>cb_chi_z bake (67ab71f)</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Strengthen descent integral so h_ez-&gt;0: bake chi_z 0.025-&gt;0.1. Does it kill the 1/z fly-away?</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>YES. chi_z=0.1: |h_ez| S1-&gt;0.107, fly-aways 35-&gt;3/300 (-91%), SP 87-&gt;97%, full gate, bit-exact. chi_z=0.2+Gamma_z=1.0 REJECTED: BETTER h_ez (0.103) but WORSE robustness (NL 25-&gt;24, fly 3-&gt;13) -- past 0.1 more loop gain OVER-DRIVES the cascade lag. h_ez-convergence and fly-away robustness DIVERGE past chi_z=0.1. The 3 residual fly = Static-IC5 mid-descent FALSE h_ez convergence (loom UNDER-reports the fast descent: measured -0.34 vs true -0.78 -&gt; h_ez looks +0.08 while truly overshooting vz 1.27 vs cmd 0.68 -&gt; sign-flip -&gt; launch)</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>chi_z=0.1 = descent optimum (the integral GAIN matters, not the izeta clamp). Superseded the LOOM_CLAMP band-aid (reverted). 3 residual = Static-IC5 perception front-end limit, not gain-tunable</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>CB57</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>cb_ez/sigz/chat/pz bake (aeb4283)</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>User: kappa IS the damping. Why isnt it damping the Z limit cycle? Can E_z engage it?</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>The Z cycle rings 100% INSIDE the boundary layer (|sigma_z|/E_z&lt;=0.2 -&gt; sat linearized -&gt; kappa switching LOCKED OUT) AND kappa_z is leaked down (0.25-&gt;0.15). E_z 1.0-&gt;0.5 engages the switching -&gt; Z cycle -8% (0.63-&gt;0.58) + better h_ez, full gate, bit-exact. E_z&lt;0.5 hard-switch OVER-DRIVES the aggressive cells (NL 25-&gt;20, fly 14; sigma_z NOISE is only 0.05 -&gt; NOT noise chatter, it is sat-saturation on large-sigma_z offset cells S3/S5/L3/C5). P_z=20 (smaller kappa) recovers 4/5 broken cells but trades damping. X/Y cycles ALSO 100% inside the layer BUT tightening E_x/E_y makes them WORSE (X 0.34-&gt;0.42) -- they are NOISE-PUMPED (s_ddot positive feedback) so kappa switching FEEDS them</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>E_z=0.5 baked (sweet spot). Z=under-damped (kappa helps via E_z), X/Y=forced/noise-pumped (kappa hurts; s_ddot-drop is the lever). DIFFERENT mechanisms -- dont apply the E_z fix to lateral</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>CB58</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>cb_latlim/aggrtune/aggr3 (lateral-limit audit)</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Does the test run hit any LIMIT in lateral control on a fast/offset target (Linear-IC3 @2x)? Retune chi_r/Gamma to catch faster targets?</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>The VISIBILITY-CBF is the limit, NOT the gains. CBF cuts commanded lateral accel to 9% of demand (100% of steps), lean 100% CONE-clamped (theta_cone not the 60deg cap), position-funnel-y rails 22%. The flow funnel S_2 is NOT saturated (0.05) -&gt; control GAINS have headroom, bottleneck is DOWNSTREAM. chi_r=2 REGRESSES the nominal set 24-&gt;18; chi_r2+cone-relax only gets xy 4.75-&gt;2.93 STILL FoV-breaching. fov_inset/theta_cap zero effect (marker leaves AHEAD because drone falls behind, not over-lean)</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>Lateral ceiling = the target-visibility CBF (the papers own guarantee) = visibility-vs-agility tradeoff hard-capped by camera FoV. NOT gain-tunable. Fix = wider FoV (hardware) or anticipatory guidance. AUDIT THE LIMITS before retuning -- gains usually have headroom</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>CB59</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>cb_yawlim/yawconv (yaw-limit audit)</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Does the test run hit a LIMIT in yaw control (Circular wz=1.0, yaw err blew to 40deg)? Increase e_a convergence to fix?</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Yaw limit = +-90deg MARKER-SYMMETRY ALIAS (virtual-compass observability). e_a hits 89.8deg (IC4) right at the unwrap edge; square marker observable only to +-90deg. The yaw ASMC switching is NOT saturated (sat max 0.89, kappa_a healthy) -&gt; gains have headroom. Inner loop yaw-rate lags (cmd 2.85 vs achieved 1.62). Faster e_a convergence (kappa_a0=5/Gamma_a=2) DOES pull e_a off the alias (89.8-&gt;49deg) BUT cant rescue wz=1.0 (lateral FoV co-binds); at wz=0.75 lateral breaches with yaw still fine (&lt;=21deg) -&gt; yaw boost is MOOT. Yaw only binds AFTER the lateral collapse drags the drone far behind</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Yaw ceiling = +-90deg observability (perception, like lateral), NOT gains. Coupled to lateral FoV failure. e_a-convergence boost real but cannot extend a lateral-bound case. At Circ wz=0.5 (clean ceiling) yaw err=2.9deg, full margin</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>CB60</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>traj_Gen aggressive baselines + cb_*sweep/finalval (UNCOMMITTED + REGEN PENDING)</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Make moving-target trajectories more aggressive while keeping 25/25 + +-40%</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>LOCKED set (5-IC 25/25 + centered +-40%, both seeds; committed 90ef528): Linear 1.1x, Sinusoidal v0=0.5 (1.67x), Lissajous w1 -0.8-&gt;-0.5 (reshaped) + w2 0.4-&gt;0.85, Circular wz=0.4 (1.6x). TWO-TEST CONVENTION (was conflated): 25/25 = 5-IC set at baseline (offset ICs bind); +-40% = CENTERED-IC speed sweep (2-3x more headroom). 5-IC ceilings: Linear 1.1x (visibility-CBF floor), Sin ~1.9x, Liss 2.5x (+25% collapses), Circ 2.0x (wz=1.0 -&gt; 0/10 on BOTH lateral FoV AND +-90 yaw alias). Linear edit-bug caught: v=2.0 with p=1.0 -&gt; v!=dp/dt corrupts rel-vel check (verify p,v same multiplier)</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>Substantially more aggressive (Liss 2.1x, Circ 1.6x, Sin 1.67x) keeping both guarantees. Linear is the floor (visibility-CBF catch-up). OPEN: +-40% centered-vs-5-IC convention. PENDING: commit traj_Gen + full dataset/figure REGEN (stale at old baselines)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/MATLAB/test_data/MATLAB_test_record.xlsx
+++ b/MATLAB/test_data/MATLAB_test_record.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cthilde_test_log" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="findings" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="combined_barrier_log" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="cthilde_test_log" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="findings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="combined_barrier_log" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1320,7 +1320,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1612,6 +1612,94 @@
       <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Align p_r_inf&gt;=1 with the proof; precision unaffected (comes from p_h/chi_r)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>F13</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>[back-filled 2026-07-02, from 2026-06-15 session] DH_D_CAP=20 bake gate (validate_cap20.m): base vs cap=20 on the canonical 5 ICs (noiseless + noisy n=5, 30 reps each) -- SP 27/30 vs 27/30, xy_med 0.017 vs 0.017, per-rep values IDENTICAL. The cap engages only on pathological V_dh_d spikes; no-regression confirmed -&gt; DH_D_CAP=20 baked (8af734a).</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>MATLAB/Datasets/validate_cap20.mat (60 rows: xy/vel/sp/land/fov x ic1-5 x ci{base,cap20}); memory feedback_ic5_cbf_strip_mechanism</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>PX4 DH_D_MAX analogue; kills the dh_d thrash that noise-weakens the CBF -Y at IC5</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>F14</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>[back-filled 2026-07-02, from 2026-06-15 session] Adaptive CoG feedforward gate (validate_cogff.m): base 27/30 SP -&gt; GAMMA_COG=0.003: 29/30, =0.005: 29/30 (tied; xy_med 0.017 -&gt; 0.005/0.006). Improves IC3/4/5, no regression on IC1/2 -&gt; GAMMA_COG 0-&gt;0.005 baked (2ec4477).</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>MATLAB/Datasets/validate_cogff.mat (90 rows: ic1-5 x ci{base,0.003,0.005} x 6 reps); memory feedback_cog_adaptive_feedforward</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>First IC5-recovering lever that passes the full IC1-5 gate; thrust-scaled Lee-style tau_ff=-T*theta_hat</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>F15</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>[back-filled 2026-07-02, from 2026-06-15/17 sessions] IC5 12-seed matched harness (sen_ic5_seedtest.m): base 9/12 SP (2 fly) vs outer-integral scaling kI=0.5: 8/12 (3 fly), kI=1.0: 2/12 (10 fly), kI&gt;=2.0: 0/12 (12 fly) vs noCOG ORACLE 11/12 (0 fly).</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>MATLAB/Datasets/sen_ic5_seedtest_last.mat (72 rows: seed1-12 x cfg{base,kI0.5-4.0,noCOG}); memory feedback_ic5_cbf_strip_mechanism</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>The IC5 binding uncertainty IS the CoG offset (oracle nearly perfect); raising the outer integral is a catastrophic dead-end</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>F16</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>[back-filled 2026-07-02, from ~2026-06-17 session] SEN-funnel sweep, final baseline arm (sen_funnel_sweep.m): 18/25 SP over IC1-5 x 5 reps; failures = IC3 FoV-fails at t~0.42 s (the CBF corner-strip era) + soft-misses; per-rep funnel residency (maxsen), saturation (ssat), breach (brc), and izeta-saturation columns recorded.</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>MATLAB/Datasets/sen_funnel_sweep_last.mat (25 rows); memory feedback_sen_authority_analysis</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Quantifies the pre-combined-barrier SEN-funnel baseline the authority analysis was run against</t>
         </is>
       </c>
     </row>

--- a/MATLAB/test_data/MATLAB_test_record.xlsx
+++ b/MATLAB/test_data/MATLAB_test_record.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="cthilde_test_log" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="findings" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="combined_barrier_log" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cthilde_test_log" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="findings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="combined_barrier_log" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="locked_yaw_hd_log" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1320,7 +1321,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1700,6 +1701,116 @@
       <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Quantifies the pre-combined-barrier SEN-funnel baseline the authority analysis was run against</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>F17</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>LOCKED kappa-engaged config baked in vdf_params.m (kappa0 .05 / N .10 / Pleak [.5;.5;1.5] / E .5 / Xi_r .3 / p_rinf .85 / theta_per_axis): 25/25 SP gate + 7x-stress 5/5 (vs 3/5 old baked) + kappa_z adapts MONOTONE 5.6x RMS (.057-&gt;.318) / 7.2x peak over the {0,1,3,5,7}x stress ladder. E gates switching DELIVERY not adaptation; E_xy=0.5 floor (lower pumps terminal velocity); p_h untightenable (funnel overtakes h_e); p_rinf floor ~0.85 (engR-&gt;1 below).</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>LK1-LK9 (locked_yaw_hd_log sheet); MATLAB/Datasets/MultiInit/kappa_adapt.mat; memory Memory/matlab/project_locked_kappa_engagement</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Funnels+kappa now ENGAGED -&gt; real disturbance margin for Gazebo; p_rinf=0.85&lt;1 needs Standing-Cond-1 manuscript framing</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>F18</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Yaw +-90deg observability ceiling: alpha = 0.5*atan2(2mu11, mu20-mu02) uses only EVEN-order (2nd) moments -&gt; invariant under 180deg -&gt; orientation observable mod 180 only; yaw_asmc's x2../2 unwrap folds e_a to +-90 and fast heading swings PIN e_a at 90 (no gain can act on unrepresentable error -- e_a stays 88-90deg across EVERY yaw param). FIX = PX4-parity weighted 2pi port (corner weights [4,3,2,1], weighted-centroid displacement = odd 1st moment disambiguates the pi-axis); verified clean 360 sweep; unwrap removed; gate 25/25.</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Y1-Y7 (locked_yaw_hd_log); Obsolete/image_feature_pre_weighted2pi.m; memory Memory/matlab/project_yaw_observability_campaign</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>MATLAB perception now matches PX4 _marker_principal_angle; yaw error is a faithful +-180 signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>F19</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Yaw-rate ceiling ~0.5 rad/s is ARCHITECTURAL, not gain-tunable: at 2x Circular yaw (0.96 rad/s) the failure is LATERAL (termEa only 14-18deg) -- s_e expressed in the drone-yaw-aligned V frame ORBITS at the yaw rate; radial convergence must ride on top of orbit-tracking and the accel budget saturates (CBF cone-sat frac 0.66-&gt;0.86) until the position funnel breaches (engR 1.16). chi_r 2-&gt;4 no help; kR_yaw=1.0 marginal (2/5, breaks oscillating-heading cases); yaw-rate FF Omega_d=u_a REVERTED (u_a is the lagged output -- circular).</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Y5-Y6, Y9 (locked_yaw_hd_log); cone-sat/engR vs yaw-mult audit</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Levers = wider accel budget or yaw-fixed lateral frame (research scope); manuscript range 0.29-0.67 rad/s sits inside the ceiling</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>F20</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Heading-yaw (tangent atan2(vy,vx)) on Sin/Liss: Sinusoidal trackable post-2pi with gentle Gamma_a=0.15 (5/5 realistic + speed; its vy=v0&gt;0 bounds the swing); Lissajous INTRACTABLE -- velocity ~vanishes at reversals (A=0.4: max|psi_dot|=32 rad/s) -&gt; ~180 snaps; rate-limited stateful heading does NOT fix (Sin regresses 4/5, Liss 1/5); larger A softens (worstXY 39-&gt;5) but 0/5 at all A. REVERTED -- traj_Gen restored (Sin/Liss non-rotating); Circular remains the yaw-exercising case (kappa_a adapts to sigma_a~0.95 -&gt; ~0.5 equilibrium).</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Y1-Y4, Y8, Y10 (locked_yaw_hd_log)</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>A non-rotating Liss target is the physically honest model; heading-yaw enablement parked, revertible from Obsolete/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>F21</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Prescribed-rate h_d (user design): h_d xy term s_dot_meas -&gt; phi_max.*S_r.*dp_r; derivative is 1000x smaller (RMS .007 vs measured s_ddot ~7) -&gt; folded into dh_d/c-term, s_ddot-drop REMOVED. Gate 25/25+25/25 noiseless, speed 20/20; A/B: standard stress equivalent (no breach occurs), BREACHING scenario (2x yaw) prescribed engR 0.76 NO-breach vs measured 1.16 breach. OPEN: formula incomplete -- s_e=phi_max*S_r*p_r =&gt; full deriv needs phi_max*(S_r_dot*p_r + S_r*dp_r); current form assumes S_r_dot=0; awaiting prescribed S_r_dot contraction law.</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Y11-Y13 (locked_yaw_hd_log); Obsolete/{position_funnel,flow_surface}_pre_prescrate.m; memory Memory/matlab/project_prescribed_rate_hd</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Bounded-on-breach h_d = recovery authority (validated); DO NOT commit/port to PX4 until the S_r_dot term is resolved</t>
         </is>
       </c>
     </row>
@@ -3680,4 +3791,794 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Trial</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Harness (cb_*.m)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>What varied</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>LK1</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>cb_engage_probe/sweep</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>nominal engagement audit on old baked config</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>funnel/kappa IDLE in nominal (engR~0.6 only at IC5); no margin for real disturbance</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>retune needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>LK2</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>cb_D_fulltest</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>config D (kappa0 .05, N .10, Pleak [.5;.5;1.5]) 5 traj x 5 IC</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>25/25 SP realistic; kappa active</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>D holds the gate</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>LK3</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>cb_kappa_reject</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>D vs old-baked under stress escalation per axis</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>kappa adapts UP under stress (kRMS_xy .07-&gt;.19) where baked stays flat; 7x stress 5/5 vs baked 3/5</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>kappa DEMONSTRABLY rejects; 7x margin</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>LK4</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>cb_E_kappa_sigma/E25_validate</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>boundary layer E_xy {0.25,0.5,1.0}</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>wide E_x=1.0 gates lateral switching (delivery); E_xy&lt;0.5 pumps terminal velocity</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>E=0.5 floor; E gates delivery NOT adaptation</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>LK5</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>cb_kappa_validate/threshold</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>KNOWN_DIST hook: Fx=3N step on [2,6]s (Static)</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>kappa_x rises +43% while force on, leak-decays after off</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>adaptation law verified against known input</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>LK6</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>cb_funnel_tighten/imgfunnel/lock_ph</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Xi_r .10-&gt;.3 + p_rinf 1.0-&gt;.85; then p_h tighten</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>pr-tight: xy .013-&gt;.011 (~15%), 25/25 held; p_h tighten FAILS (funnel overtakes h_e convergence, 14/25)</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>bake pr-tight; p_h untightenable</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>LK7</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>cb_lock_fulltest</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>LOCKED (D + E.5 + pr-tight) full manuscript battery</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>25/25 gate + speed 40/40 (+-40%) + multi-init 50/50 + comparison Proposed SP all</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>LOCKED baked into vdf_params</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>LK8</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>cb_pr_reduce</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>p_rinf {0.85,0.70,0.60,0.50} below the bake</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>lower p_rinf -&gt; maxEngR climbs toward 1 (breach margin gone); no precision gain worth it</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0.85 = floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>LK9</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>cb_lock_kappa/cb_kappa_adapt_data</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>kappa vs disturbance ladder {0,1,3,5,7}x, 10 cells</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>kappa_z RMS .057/.073/.137/.220/.318 MONOTONE (5.6x); peak 7.2x; x 2.7x, y 1.7x (peak)</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>genuine adaptation; kappa_adapt.mat</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>LK10</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>cb_gamma_why/cb_au_decomp</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>why Gamma can't replace kappa (terminal balloon mechanics)</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>switching term theta*sat*kappa = 94% of terminal a_u spike; reaching a_u 47.3 @Gamma=2 vs 10.4 baked (G_2^-1 amplification)</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Gamma over-drives; kappa is the right lever</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Y1</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>(traj_Gen heading yaw)</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>tangent heading atan2(vy,vx) on Sin/Liss</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Sin: realistic 5/5, speed 5/5, noiseless 4/5; Liss: 0/3 fly-away (~180deg heading snaps)</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Sin near-works; Liss pathological</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Y2</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>cb_yawret</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>yaw-gain screen on Sin noiseless failure</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>gentler recovers (Gamma_a .15 -&gt; 5/5, E_a 8 -&gt; 5/5); faster (Gamma_a .5, Omega_a .5) -&gt; 3/5</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>failure = yaw-&gt;lateral PUMP, not lag</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Y3</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>cb_yawlag/cb_yawlc</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>trace target/drone yaw + limit-cycle check</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>drone swings 140deg vs target 77deg (~90deg phase lag, overshoot); sat(sigma_a/E_a) frac 0.00, rate flips 4-6</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>bandwidth-limited FORCED track; NO limit cycle</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Y4</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>cb_eaconv</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>e_a convergence per 2s window</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>amplitude steady 20-90deg ALL windows to touchdown; peaks pinned at 90deg</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>bounded NOT converging; 90deg = observability ceiling</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Y5</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>cb_kryaw/cb_yawall</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>kR_yaw {0.5-2.5}, kOmega_yaw {0.1-0.6}, all ASMC levers</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>e_a stays 88-90deg at EVERY setting; kR_yaw&gt;=1 breaks Sin (3/5); kOmega_yaw pinned 0.2 (down=cycle, up=lag)</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>NO gain reduces the lag; inner levers exhausted</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Y6</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>(so3_tracker yaw FF)</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Omega_d=[0;0;u_a] feedforward</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Circular helped (e_a 53deg, 5/5); Sin 5/5-&gt;3/5 (u_a = lagged output, FF amplifies the swing)</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>REVERTED; circular feedback</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Y7</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>cb_rotsweep + gate</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2pi weighted-corner orientation port (PX4 parity) + unwrap removal</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>synthetic 360 sweep CLEAN (15deg steps, no fold); full gate 25/25 realistic + 25/25 noiseless; alpha_d auto-correct (Static termEa -0.0deg)</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>2pi orientation KEPT (uncommitted)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Y8</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>cb_yawtune/cb_yawterm</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>post-2pi gentle retune + terminal-lag levers</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Ga.15/Oa.15/Ea6 all recover Sin heading-yaw 5/5; Omega_a=0.4 cuts Circ termEa 17-&gt;9deg but Sin 41-&gt;60deg (windup on oscillating ref)</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>gentle linear yaw wins; integral only for constant yaw</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Y9</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>cb_circyaw/cb_coupling/cb_caps/cb_chitest/cb_kryaw2</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Circular yaw-rate mult {1,2,3,4,6}x + cap audit</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1x 5/5 -&gt; 2x 1/5 -&gt; 3x+ 0/5; s_e ORBITS at yaw rate; cone-sat frac .66/.71/.86; funnel breach engR 1.16 @2x; chi_r 2-4 flat; kR_yaw1.0 2/5</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>~0.5 rad/s ceiling ARCHITECTURAL (frame coupling + accel budget)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Y10</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>cb_wmax/cb_lissA*/cb_relax</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>rate-limited stateful heading (w_max .05-.4) + Liss A/freq relax</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>rate-limit does NOT fix (Sin 4/5 all w_max; Liss 1/5); bigger A softens raw-heading severity (worstXY 39-&gt;5) but 0/5</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>REVERTED -- traj_Gen restored; Liss stays non-rotating</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Y11</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>cb_dhd/cb_presc/cb_fold/cb_sinliss</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>prescribed-rate h_d: s_dot_meas -&gt; phi_max.*S_r.*dp_r, then folded into dh_d</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>d(s_dot_presc)/dt RMS .007 vs measured s_ddot ~7 (1000x smaller) -&gt; s_ddot-drop removed; gate 25/25 + 25/25 noiseless (baked gains)</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>smooth + consistent h_d/dh_d; validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Y12</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>cb_ab/cb_ab2</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>A/B prescribed vs measured h_d, same seeds</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>standard stress 1-7x EQUIVALENT (5/5 both, engR .59, no breach); BREACHING 2x-yaw: prescribed engR .76 NO-breach + worstXY 1.12 vs measured 1.16 breach + 1.56; speed sweep 20/20</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>bounded-on-breach benefit CONFIRMED</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Y13</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>(user review)</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>formula audit of s_dot_presc</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>phi_max.*S_r.*dp_r assumes S_r CONSTANT; s_e=phi_max*S_r*p_r =&gt; missing phi_max*S_r_dot*p_r term; measured S_r_dot would collapse to s_dot_meas (circular)</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>OPEN -- awaiting prescribed S_r_dot contraction law</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/MATLAB/test_data/MATLAB_test_record.xlsx
+++ b/MATLAB/test_data/MATLAB_test_record.xlsx
@@ -3799,7 +3799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -4578,6 +4578,38 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>cb_px4port</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>PX4 GT-FB bakes on the MATLAB gate: Gamma_xy=0.25, Xi_h=[0.7,0.7,1.0], both (vs baked LOCKED)</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>baked 25/25 (mXY .011, 7x 5/5); Gxy.25 23/25 worstXY 2.63 (reaching-starved in engaged-funnel design); Xih 22/25 + 7x 1/5 (p_h-overtake via contraction rate); both 19/25 + 7x 0/5. Already-converged: N=.10, P2INF_xy=1.0, cbf2-only, no backstepping h_d</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>PX4 bakes REJECTED on MATLAB -- regime-specific (wide-funnel PR0=10 vs engaged p_r0=1.2); divergences stand documented</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/MATLAB/test_data/MATLAB_test_record.xlsx
+++ b/MATLAB/test_data/MATLAB_test_record.xlsx
@@ -1800,17 +1800,17 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Prescribed-rate h_d (user design): h_d xy term s_dot_meas -&gt; phi_max.*S_r.*dp_r; derivative is 1000x smaller (RMS .007 vs measured s_ddot ~7) -&gt; folded into dh_d/c-term, s_ddot-drop REMOVED. Gate 25/25+25/25 noiseless, speed 20/20; A/B: standard stress equivalent (no breach occurs), BREACHING scenario (2x yaw) prescribed engR 0.76 NO-breach vs measured 1.16 breach. OPEN: formula incomplete -- s_e=phi_max*S_r*p_r =&gt; full deriv needs phi_max*(S_r_dot*p_r + S_r*dp_r); current form assumes S_r_dot=0; awaiting prescribed S_r_dot contraction law.</t>
+          <t>Prescribed-rate h_d (user design): h_d xy term s_dot_meas -&gt; phi_max.*S_r.*dp_r; derivative is 1000x smaller (RMS .007 vs measured s_ddot ~7) -&gt; folded into dh_d/c-term, s_ddot-drop REMOVED. Gate 25/25+25/25 noiseless, speed 20/20; A/B: standard stress equivalent (no breach occurs), BREACHING scenario (2x yaw) prescribed engR 0.76 NO-breach vs measured 1.16 breach. RESOLVED (Y14): formula complete as a DEFINITION -- h_e,xy = p_10*zeta_r_dot/g_r (S_r varying IS the signal; S_r_dot law rejected as wrong approach); finite-diff dh_d kept per user.</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Y11-Y13 (locked_yaw_hd_log); Obsolete/{position_funnel,flow_surface}_pre_prescrate.m; memory Memory/matlab/project_prescribed_rate_hd</t>
+          <t>Y11-Y14 (locked_yaw_hd_log); Obsolete/{position_funnel,flow_surface}_pre_prescrate.m; memory Memory/matlab/project_prescribed_rate_hd</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Bounded-on-breach h_d = recovery authority (validated); DO NOT commit/port to PX4 until the S_r_dot term is resolved</t>
+          <t>Bounded-on-breach h_d = recovery authority (validated); MATLAB form final (016855e); PX4 port = separate decision</t>
         </is>
       </c>
     </row>
@@ -3799,7 +3799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -4574,37 +4574,69 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>OPEN -- awaiting prescribed S_r_dot contraction law</t>
+          <t>OPEN -- S_r_dot question raised</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>Y14</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>(user resolution)</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>S_r_dot contraction law proposal REJECTED by user (wrong approach)</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>correct reading: h_d = p_10*S_r*p_r_dot is the funnel-consistent reference by DEFINITION; S_r varying is the SIGNAL -- h_e,xy = sdot - p_10*S_r*p_r_dot = p_10*zeta_r_dot/g_r (barrier-coordinate rate; sigma = true PD pair on zeta_r). A prescribed S_r_dot would make the reference the convergence driver (violates funnel-as-constraint). dh_d: finite-diff kept per user (tiny S_r_dot content RMS .007, gate-validated) over analytic S_r-frozen</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>RESOLVED -- formula complete; code final at 016855e</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>cb_px4port</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>PX4 GT-FB bakes on the MATLAB gate: Gamma_xy=0.25, Xi_h=[0.7,0.7,1.0], both (vs baked LOCKED)</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>baked 25/25 (mXY .011, 7x 5/5); Gxy.25 23/25 worstXY 2.63 (reaching-starved in engaged-funnel design); Xih 22/25 + 7x 1/5 (p_h-overtake via contraction rate); both 19/25 + 7x 0/5. Already-converged: N=.10, P2INF_xy=1.0, cbf2-only, no backstepping h_d</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>PX4 bakes REJECTED on MATLAB -- regime-specific (wide-funnel PR0=10 vs engaged p_r0=1.2); divergences stand documented</t>
         </is>
